--- a/data/last_week_comparisson.xlsx
+++ b/data/last_week_comparisson.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5052e625e7f51e50/Desktop/dengue_dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E2AAAC71-6BB4-448D-8BD6-3B653E2E87BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{E2AAAC71-6BB4-448D-8BD6-3B653E2E87BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD113359-536C-413D-AED5-FBEEF94F36A5}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E377CF4B-C8B3-4010-9F12-B4310FC3BC97}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{E377CF4B-C8B3-4010-9F12-B4310FC3BC97}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,17 +34,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>district</t>
   </si>
   <si>
-    <t>2025_26th</t>
-  </si>
-  <si>
-    <t>2026_26th</t>
-  </si>
-  <si>
     <t>deaths2026</t>
   </si>
   <si>
@@ -124,6 +118,15 @@
   </si>
   <si>
     <t>Kegalle</t>
+  </si>
+  <si>
+    <t>total_2026</t>
+  </si>
+  <si>
+    <t>2025_29th</t>
+  </si>
+  <si>
+    <t>2026_29th</t>
   </si>
 </sst>
 </file>
@@ -166,9 +169,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -483,385 +487,466 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4ECA8DE4-0AA0-4044-A091-81793926F517}">
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B2" s="1">
+        <v>297</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1535</v>
+      </c>
+      <c r="D2" s="1">
+        <v>14</v>
+      </c>
+      <c r="E2" s="1">
+        <v>18172</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="B3" s="1">
+        <v>198</v>
+      </c>
+      <c r="C3" s="1">
+        <v>1814</v>
+      </c>
+      <c r="D3" s="1">
+        <v>10</v>
+      </c>
+      <c r="E3" s="1">
+        <v>15910</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1">
-        <v>329</v>
-      </c>
-      <c r="C2" s="1">
-        <v>1174</v>
-      </c>
-      <c r="D2" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="B4" s="1">
+        <v>50</v>
+      </c>
+      <c r="C4" s="1">
+        <v>524</v>
+      </c>
+      <c r="D4" s="1">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1">
+        <v>5920</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="1">
-        <v>193</v>
-      </c>
-      <c r="C3" s="1">
-        <v>1750</v>
-      </c>
-      <c r="D3" s="1">
+      <c r="B5" s="1">
+        <v>160</v>
+      </c>
+      <c r="C5" s="1">
+        <v>660</v>
+      </c>
+      <c r="D5" s="1">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1">
+        <v>5108</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="1">
-        <v>74</v>
-      </c>
-      <c r="C4" s="1">
-        <v>463</v>
-      </c>
-      <c r="D4" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="B6" s="1">
+        <v>20</v>
+      </c>
+      <c r="C6" s="1">
+        <v>77</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0</v>
+      </c>
+      <c r="E6" s="1">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="1">
-        <v>172</v>
-      </c>
-      <c r="C5" s="1">
-        <v>486</v>
-      </c>
-      <c r="D5" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+      <c r="B7" s="1">
+        <v>23</v>
+      </c>
+      <c r="C7" s="1">
+        <v>95</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0</v>
+      </c>
+      <c r="E7" s="1">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="1">
-        <v>16</v>
-      </c>
-      <c r="C6" s="1">
-        <v>42</v>
-      </c>
-      <c r="D6" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="1">
-        <v>6</v>
-      </c>
-      <c r="C7" s="1">
-        <v>50</v>
-      </c>
-      <c r="D7" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="B8" s="1">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="C8" s="1">
-        <v>247</v>
+        <v>322</v>
       </c>
       <c r="D8" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E8" s="1">
+        <v>4270</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B9" s="1">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C9" s="1">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="D9" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E9" s="1">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="1">
+        <v>25</v>
+      </c>
+      <c r="C10" s="1">
+        <v>454</v>
+      </c>
+      <c r="D10" s="1">
+        <v>4</v>
+      </c>
+      <c r="E10" s="1">
+        <v>5327</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="1">
+        <v>43</v>
+      </c>
+      <c r="C11" s="1">
+        <v>55</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0</v>
+      </c>
+      <c r="E11" s="1">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="1">
-        <v>45</v>
-      </c>
-      <c r="C10" s="1">
-        <v>364</v>
-      </c>
-      <c r="D10" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
+      <c r="B12" s="1">
+        <v>3</v>
+      </c>
+      <c r="C12" s="1">
+        <v>6</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0</v>
+      </c>
+      <c r="E12" s="1">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="1">
-        <v>6</v>
-      </c>
-      <c r="C11" s="1">
-        <v>26</v>
-      </c>
-      <c r="D11" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
+      <c r="B13" s="1">
+        <v>2</v>
+      </c>
+      <c r="C13" s="1">
         <v>14</v>
       </c>
-      <c r="B12" s="1">
-        <v>1</v>
-      </c>
-      <c r="C12" s="1">
-        <v>5</v>
-      </c>
-      <c r="D12" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
+      <c r="D13" s="1">
+        <v>0</v>
+      </c>
+      <c r="E13" s="1">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="1">
+        <v>3</v>
+      </c>
+      <c r="C14" s="1">
+        <v>11</v>
+      </c>
+      <c r="D14" s="1">
+        <v>0</v>
+      </c>
+      <c r="E14" s="1">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="1">
-        <v>0</v>
-      </c>
-      <c r="C13" s="1">
+      <c r="B15" s="2">
+        <v>0</v>
+      </c>
+      <c r="C15" s="1">
         <v>7</v>
       </c>
-      <c r="D13" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
+      <c r="D15" s="1">
+        <v>0</v>
+      </c>
+      <c r="E15" s="1">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="1">
-        <v>0</v>
-      </c>
-      <c r="C14" s="1">
-        <v>4</v>
-      </c>
-      <c r="D14" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" s="1">
-        <v>1</v>
-      </c>
-      <c r="C15" s="1">
-        <v>1</v>
-      </c>
-      <c r="D15" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="B16" s="1">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C16" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E16" s="1">
+        <v>1324</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B17" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C17" s="1">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D17" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E17" s="1">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B18" s="1">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C18" s="1">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D18" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E18" s="1">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="1">
+        <v>6</v>
+      </c>
+      <c r="C19" s="1">
+        <v>51</v>
+      </c>
+      <c r="D19" s="1">
+        <v>0</v>
+      </c>
+      <c r="E19" s="1">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="1">
+        <v>53</v>
+      </c>
+      <c r="C20" s="1">
+        <v>256</v>
+      </c>
+      <c r="D20" s="1">
+        <v>2</v>
+      </c>
+      <c r="E20" s="1">
+        <v>2090</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="1">
-        <v>7</v>
-      </c>
-      <c r="C19" s="1">
-        <v>43</v>
-      </c>
-      <c r="D19" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20" s="1">
-        <v>41</v>
-      </c>
-      <c r="C20" s="1">
-        <v>184</v>
-      </c>
-      <c r="D20" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="B21" s="1">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C21" s="1">
-        <v>171</v>
+        <v>231</v>
       </c>
       <c r="D21" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E21" s="1">
+        <v>1572</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B22" s="1">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C22" s="1">
-        <v>95</v>
+        <v>128</v>
       </c>
       <c r="D22" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="E22" s="1">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B23" s="1">
         <v>9</v>
       </c>
       <c r="C23" s="1">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="D23" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="E23" s="1">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" s="1">
+        <v>28</v>
+      </c>
+      <c r="C24" s="1">
+        <v>114</v>
+      </c>
+      <c r="D24" s="1">
+        <v>0</v>
+      </c>
+      <c r="E24" s="1">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" s="1">
+        <v>10</v>
+      </c>
+      <c r="C25" s="1">
+        <v>93</v>
+      </c>
+      <c r="D25" s="1">
+        <v>0</v>
+      </c>
+      <c r="E25" s="1">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="1">
-        <v>14</v>
-      </c>
-      <c r="C24" s="1">
-        <v>97</v>
-      </c>
-      <c r="D24" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
+      <c r="B26" s="1">
+        <v>83</v>
+      </c>
+      <c r="C26" s="1">
+        <v>344</v>
+      </c>
+      <c r="D26" s="1">
+        <v>3</v>
+      </c>
+      <c r="E26" s="1">
+        <v>4291</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="1">
-        <v>13</v>
-      </c>
-      <c r="C25" s="1">
-        <v>88</v>
-      </c>
-      <c r="D25" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B26" s="1">
-        <v>107</v>
-      </c>
-      <c r="C26" s="1">
-        <v>193</v>
-      </c>
-      <c r="D26" s="1">
+      <c r="B27" s="1">
+        <v>24</v>
+      </c>
+      <c r="C27" s="1">
+        <v>225</v>
+      </c>
+      <c r="D27" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B27" s="1">
-        <v>38</v>
-      </c>
-      <c r="C27" s="1">
-        <v>192</v>
-      </c>
-      <c r="D27" s="1">
-        <v>0</v>
+      <c r="E27" s="1">
+        <v>2067</v>
       </c>
     </row>
   </sheetData>
